--- a/Pasta_2.xlsx
+++ b/Pasta_2.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\DAM\site_dados\webScrapping_dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2410" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2470" uniqueCount="76">
   <si>
     <t>INEP</t>
   </si>
@@ -248,11 +248,17 @@
   <si>
     <t>9° ANO</t>
   </si>
+  <si>
+    <t>MARACANAÚ</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -303,7 +309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -319,6 +325,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -622,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:Q799"/>
+  <dimension ref="B1:Q819"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
@@ -39046,6 +39055,966 @@
       </c>
       <c r="Q799" s="3"/>
     </row>
+    <row r="800" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B800" s="3">
+        <v>2307650</v>
+      </c>
+      <c r="C800" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D800" s="3">
+        <v>2017</v>
+      </c>
+      <c r="E800" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F800" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G800" s="3">
+        <v>12.97</v>
+      </c>
+      <c r="H800" s="3">
+        <v>11.41</v>
+      </c>
+      <c r="I800" s="3">
+        <v>16.61</v>
+      </c>
+      <c r="J800" s="3">
+        <v>20.440000000000001</v>
+      </c>
+      <c r="K800" s="3">
+        <v>19.27</v>
+      </c>
+      <c r="L800" s="3">
+        <v>12.77</v>
+      </c>
+      <c r="M800" s="3">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="N800" s="3">
+        <v>1.79</v>
+      </c>
+      <c r="O800" s="3">
+        <v>0</v>
+      </c>
+      <c r="P800" s="3"/>
+      <c r="Q800" s="3"/>
+    </row>
+    <row r="801" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B801" s="3">
+        <v>2307650</v>
+      </c>
+      <c r="C801" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D801" s="3">
+        <v>2017</v>
+      </c>
+      <c r="E801" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F801" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G801" s="3">
+        <v>13.790000000000001</v>
+      </c>
+      <c r="H801" s="3">
+        <v>14.72</v>
+      </c>
+      <c r="I801" s="3">
+        <v>20.94</v>
+      </c>
+      <c r="J801" s="3">
+        <v>19.39</v>
+      </c>
+      <c r="K801" s="3">
+        <v>16.07</v>
+      </c>
+      <c r="L801" s="3">
+        <v>9.11</v>
+      </c>
+      <c r="M801" s="3">
+        <v>3.99</v>
+      </c>
+      <c r="N801" s="3">
+        <v>1.71</v>
+      </c>
+      <c r="O801" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="P801" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="Q801" s="3"/>
+    </row>
+    <row r="802" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B802" s="3">
+        <v>2307650</v>
+      </c>
+      <c r="C802" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D802" s="3">
+        <v>2019</v>
+      </c>
+      <c r="E802" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F802" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G802" s="3">
+        <v>8.58</v>
+      </c>
+      <c r="H802" s="3">
+        <v>8.89</v>
+      </c>
+      <c r="I802" s="3">
+        <v>14.94</v>
+      </c>
+      <c r="J802" s="3">
+        <v>20.52</v>
+      </c>
+      <c r="K802" s="3">
+        <v>19.73</v>
+      </c>
+      <c r="L802" s="3">
+        <v>16.66</v>
+      </c>
+      <c r="M802" s="3">
+        <v>8.15</v>
+      </c>
+      <c r="N802" s="3">
+        <v>2.48</v>
+      </c>
+      <c r="O802" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="P802" s="3"/>
+      <c r="Q802" s="3"/>
+    </row>
+    <row r="803" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B803" s="3">
+        <v>2307650</v>
+      </c>
+      <c r="C803" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D803" s="3">
+        <v>2019</v>
+      </c>
+      <c r="E803" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F803" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G803" s="3">
+        <v>10.31</v>
+      </c>
+      <c r="H803" s="3">
+        <v>10.72</v>
+      </c>
+      <c r="I803" s="3">
+        <v>16.18</v>
+      </c>
+      <c r="J803" s="3">
+        <v>20.7</v>
+      </c>
+      <c r="K803" s="3">
+        <v>19.27</v>
+      </c>
+      <c r="L803" s="3">
+        <v>13.71</v>
+      </c>
+      <c r="M803" s="3">
+        <v>6.5200000000000005</v>
+      </c>
+      <c r="N803" s="3">
+        <v>1.98</v>
+      </c>
+      <c r="O803" s="3">
+        <v>0.61</v>
+      </c>
+      <c r="P803" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q803" s="3"/>
+    </row>
+    <row r="804" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B804" s="3">
+        <v>2307650</v>
+      </c>
+      <c r="C804" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D804" s="3">
+        <v>2021</v>
+      </c>
+      <c r="E804" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F804" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G804" s="3">
+        <v>11.59</v>
+      </c>
+      <c r="H804" s="3">
+        <v>11.33</v>
+      </c>
+      <c r="I804" s="3">
+        <v>16.41</v>
+      </c>
+      <c r="J804" s="3">
+        <v>19.89</v>
+      </c>
+      <c r="K804" s="3">
+        <v>19.07</v>
+      </c>
+      <c r="L804" s="3">
+        <v>13.370000000000001</v>
+      </c>
+      <c r="M804" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="N804" s="3">
+        <v>1.76</v>
+      </c>
+      <c r="O804" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="P804" s="3"/>
+      <c r="Q804" s="3"/>
+    </row>
+    <row r="805" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B805" s="3">
+        <v>2307650</v>
+      </c>
+      <c r="C805" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D805" s="3">
+        <v>2021</v>
+      </c>
+      <c r="E805" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F805" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G805" s="3">
+        <v>14.38</v>
+      </c>
+      <c r="H805" s="3">
+        <v>15.200000000000001</v>
+      </c>
+      <c r="I805" s="3">
+        <v>19.47</v>
+      </c>
+      <c r="J805" s="3">
+        <v>19.78</v>
+      </c>
+      <c r="K805" s="3">
+        <v>17.77</v>
+      </c>
+      <c r="L805" s="3">
+        <v>9.7100000000000009</v>
+      </c>
+      <c r="M805" s="3">
+        <v>2.83</v>
+      </c>
+      <c r="N805" s="3">
+        <v>0.65</v>
+      </c>
+      <c r="O805" s="3">
+        <v>0.21</v>
+      </c>
+      <c r="P805" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q805" s="3"/>
+    </row>
+    <row r="806" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B806" s="3">
+        <v>2307650</v>
+      </c>
+      <c r="C806" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D806" s="3">
+        <v>2023</v>
+      </c>
+      <c r="E806" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F806" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G806" s="3">
+        <v>13.05</v>
+      </c>
+      <c r="H806" s="3">
+        <v>10.85</v>
+      </c>
+      <c r="I806" s="3">
+        <v>13.74</v>
+      </c>
+      <c r="J806" s="3">
+        <v>17.18</v>
+      </c>
+      <c r="K806" s="3">
+        <v>19.68</v>
+      </c>
+      <c r="L806" s="3">
+        <v>15.26</v>
+      </c>
+      <c r="M806" s="3">
+        <v>7.82</v>
+      </c>
+      <c r="N806" s="3">
+        <v>2.21</v>
+      </c>
+      <c r="O806" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="P806" s="3"/>
+      <c r="Q806" s="3"/>
+    </row>
+    <row r="807" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B807" s="3">
+        <v>2307650</v>
+      </c>
+      <c r="C807" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D807" s="3">
+        <v>2023</v>
+      </c>
+      <c r="E807" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F807" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G807" s="3">
+        <v>13.48</v>
+      </c>
+      <c r="H807" s="3">
+        <v>15.25</v>
+      </c>
+      <c r="I807" s="3">
+        <v>18.2</v>
+      </c>
+      <c r="J807" s="3">
+        <v>18.71</v>
+      </c>
+      <c r="K807" s="3">
+        <v>16.73</v>
+      </c>
+      <c r="L807" s="3">
+        <v>10.47</v>
+      </c>
+      <c r="M807" s="3">
+        <v>4.74</v>
+      </c>
+      <c r="N807" s="3">
+        <v>1.79</v>
+      </c>
+      <c r="O807" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="P807" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="Q807" s="3"/>
+    </row>
+    <row r="808" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B808" s="3">
+        <v>2307650</v>
+      </c>
+      <c r="C808" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D808" s="3">
+        <v>2017</v>
+      </c>
+      <c r="E808" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F808" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G808" s="3">
+        <v>0</v>
+      </c>
+      <c r="H808" s="3">
+        <v>7.43</v>
+      </c>
+      <c r="I808" s="3">
+        <v>12.18</v>
+      </c>
+      <c r="J808" s="3">
+        <v>16.13</v>
+      </c>
+      <c r="K808" s="3">
+        <v>19.53</v>
+      </c>
+      <c r="L808" s="3">
+        <v>18.77</v>
+      </c>
+      <c r="M808" s="3">
+        <v>12.96</v>
+      </c>
+      <c r="N808" s="3">
+        <v>6.54</v>
+      </c>
+      <c r="O808" s="3">
+        <v>2.67</v>
+      </c>
+      <c r="P808" s="3">
+        <v>0.68</v>
+      </c>
+      <c r="Q808" s="3"/>
+    </row>
+    <row r="809" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B809" s="3">
+        <v>2307650</v>
+      </c>
+      <c r="C809" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D809" s="3">
+        <v>2017</v>
+      </c>
+      <c r="E809" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F809" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G809" s="3">
+        <v>1.07</v>
+      </c>
+      <c r="H809" s="3">
+        <v>5.54</v>
+      </c>
+      <c r="I809" s="3">
+        <v>11.92</v>
+      </c>
+      <c r="J809" s="3">
+        <v>18.830000000000002</v>
+      </c>
+      <c r="K809" s="3">
+        <v>20.68</v>
+      </c>
+      <c r="L809" s="3">
+        <v>17.86</v>
+      </c>
+      <c r="M809" s="3">
+        <v>12.47</v>
+      </c>
+      <c r="N809" s="3">
+        <v>7.19</v>
+      </c>
+      <c r="O809" s="3">
+        <v>3.11</v>
+      </c>
+      <c r="P809" s="3">
+        <v>1.02</v>
+      </c>
+      <c r="Q809" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="810" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B810" s="3">
+        <v>2307650</v>
+      </c>
+      <c r="C810" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D810" s="3">
+        <v>2019</v>
+      </c>
+      <c r="E810" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F810" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G810" s="3">
+        <v>3.34</v>
+      </c>
+      <c r="H810" s="3">
+        <v>6.67</v>
+      </c>
+      <c r="I810" s="3">
+        <v>10.88</v>
+      </c>
+      <c r="J810" s="3">
+        <v>15.870000000000001</v>
+      </c>
+      <c r="K810" s="3">
+        <v>19.36</v>
+      </c>
+      <c r="L810" s="3">
+        <v>17.27</v>
+      </c>
+      <c r="M810" s="3">
+        <v>14.47</v>
+      </c>
+      <c r="N810" s="3">
+        <v>7.72</v>
+      </c>
+      <c r="O810" s="3">
+        <v>3.5500000000000003</v>
+      </c>
+      <c r="P810" s="3">
+        <v>0.86</v>
+      </c>
+      <c r="Q810" s="3"/>
+    </row>
+    <row r="811" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B811" s="3">
+        <v>2307650</v>
+      </c>
+      <c r="C811" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D811" s="3">
+        <v>2019</v>
+      </c>
+      <c r="E811" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F811" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G811" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="H811" s="3">
+        <v>3.83</v>
+      </c>
+      <c r="I811" s="3">
+        <v>11.18</v>
+      </c>
+      <c r="J811" s="3">
+        <v>17.86</v>
+      </c>
+      <c r="K811" s="3">
+        <v>19.760000000000002</v>
+      </c>
+      <c r="L811" s="3">
+        <v>18.12</v>
+      </c>
+      <c r="M811" s="3">
+        <v>14.92</v>
+      </c>
+      <c r="N811" s="3">
+        <v>7.9300000000000006</v>
+      </c>
+      <c r="O811" s="3">
+        <v>3.97</v>
+      </c>
+      <c r="P811" s="3">
+        <v>1.44</v>
+      </c>
+      <c r="Q811" s="3">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="812" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B812" s="3">
+        <v>2307650</v>
+      </c>
+      <c r="C812" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D812" s="3">
+        <v>2021</v>
+      </c>
+      <c r="E812" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F812" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G812" s="3">
+        <v>5.1000000000000005</v>
+      </c>
+      <c r="H812" s="3">
+        <v>9.1300000000000008</v>
+      </c>
+      <c r="I812" s="3">
+        <v>13.32</v>
+      </c>
+      <c r="J812" s="3">
+        <v>15.450000000000001</v>
+      </c>
+      <c r="K812" s="3">
+        <v>17.420000000000002</v>
+      </c>
+      <c r="L812" s="3">
+        <v>17.75</v>
+      </c>
+      <c r="M812" s="3">
+        <v>12.23</v>
+      </c>
+      <c r="N812" s="3">
+        <v>6.65</v>
+      </c>
+      <c r="O812" s="3">
+        <v>2.73</v>
+      </c>
+      <c r="P812" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="Q812" s="3"/>
+    </row>
+    <row r="813" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B813" s="3">
+        <v>2307650</v>
+      </c>
+      <c r="C813" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D813" s="3">
+        <v>2021</v>
+      </c>
+      <c r="E813" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F813" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G813" s="3">
+        <v>1.69</v>
+      </c>
+      <c r="H813" s="3">
+        <v>7.03</v>
+      </c>
+      <c r="I813" s="3">
+        <v>15.52</v>
+      </c>
+      <c r="J813" s="3">
+        <v>20.89</v>
+      </c>
+      <c r="K813" s="3">
+        <v>21.29</v>
+      </c>
+      <c r="L813" s="3">
+        <v>16.330000000000002</v>
+      </c>
+      <c r="M813" s="3">
+        <v>10.17</v>
+      </c>
+      <c r="N813" s="3">
+        <v>4.51</v>
+      </c>
+      <c r="O813" s="3">
+        <v>1.9100000000000001</v>
+      </c>
+      <c r="P813" s="3">
+        <v>0.65</v>
+      </c>
+      <c r="Q813" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="814" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B814" s="3">
+        <v>2307650</v>
+      </c>
+      <c r="C814" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D814" s="3">
+        <v>2023</v>
+      </c>
+      <c r="E814" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F814" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G814" s="3">
+        <v>2.77</v>
+      </c>
+      <c r="H814" s="3">
+        <v>6.42</v>
+      </c>
+      <c r="I814" s="3">
+        <v>8.74</v>
+      </c>
+      <c r="J814" s="3">
+        <v>12.31</v>
+      </c>
+      <c r="K814" s="3">
+        <v>17.25</v>
+      </c>
+      <c r="L814" s="3">
+        <v>18.96</v>
+      </c>
+      <c r="M814" s="3">
+        <v>15.27</v>
+      </c>
+      <c r="N814" s="3">
+        <v>10.58</v>
+      </c>
+      <c r="O814" s="3">
+        <v>5.25</v>
+      </c>
+      <c r="P814" s="3">
+        <v>2.46</v>
+      </c>
+      <c r="Q814" s="3"/>
+    </row>
+    <row r="815" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B815" s="3">
+        <v>2307650</v>
+      </c>
+      <c r="C815" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D815" s="3">
+        <v>2023</v>
+      </c>
+      <c r="E815" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F815" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G815" s="3">
+        <v>1.42</v>
+      </c>
+      <c r="H815" s="3">
+        <v>5.09</v>
+      </c>
+      <c r="I815" s="3">
+        <v>9.61</v>
+      </c>
+      <c r="J815" s="3">
+        <v>15.84</v>
+      </c>
+      <c r="K815" s="3">
+        <v>19.080000000000002</v>
+      </c>
+      <c r="L815" s="3">
+        <v>16.21</v>
+      </c>
+      <c r="M815" s="3">
+        <v>13.030000000000001</v>
+      </c>
+      <c r="N815" s="3">
+        <v>10.26</v>
+      </c>
+      <c r="O815" s="3">
+        <v>6.26</v>
+      </c>
+      <c r="P815" s="3">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="Q815" s="3">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="816" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B816" s="3">
+        <v>2307650</v>
+      </c>
+      <c r="C816" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D816" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E816" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F816" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G816" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="H816" s="6">
+        <v>3.97</v>
+      </c>
+      <c r="I816" s="6">
+        <v>6.87</v>
+      </c>
+      <c r="J816" s="6">
+        <v>11.59</v>
+      </c>
+      <c r="K816" s="6">
+        <v>17.330000000000002</v>
+      </c>
+      <c r="L816" s="6">
+        <v>18.68</v>
+      </c>
+      <c r="M816" s="6">
+        <v>17.740000000000002</v>
+      </c>
+      <c r="N816" s="6">
+        <v>13.11</v>
+      </c>
+      <c r="O816" s="6">
+        <v>7.16</v>
+      </c>
+      <c r="P816" s="6">
+        <v>2.23</v>
+      </c>
+      <c r="Q816" s="6"/>
+    </row>
+    <row r="817" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B817" s="3">
+        <v>2307650</v>
+      </c>
+      <c r="C817" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D817" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E817" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F817" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G817" s="6">
+        <v>1.46</v>
+      </c>
+      <c r="H817" s="6">
+        <v>3.09</v>
+      </c>
+      <c r="I817" s="6">
+        <v>5.92</v>
+      </c>
+      <c r="J817" s="6">
+        <v>12.31</v>
+      </c>
+      <c r="K817" s="6">
+        <v>16.32</v>
+      </c>
+      <c r="L817" s="6">
+        <v>18.07</v>
+      </c>
+      <c r="M817" s="6">
+        <v>16.740000000000002</v>
+      </c>
+      <c r="N817" s="6">
+        <v>12.950000000000001</v>
+      </c>
+      <c r="O817" s="6">
+        <v>7.67</v>
+      </c>
+      <c r="P817" s="6">
+        <v>4.09</v>
+      </c>
+      <c r="Q817" s="6">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="818" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B818" s="3">
+        <v>2307650</v>
+      </c>
+      <c r="C818" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D818" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E818" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F818" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G818" s="6">
+        <v>13.02</v>
+      </c>
+      <c r="H818" s="6">
+        <v>11.43</v>
+      </c>
+      <c r="I818" s="6">
+        <v>13.94</v>
+      </c>
+      <c r="J818" s="6">
+        <v>16.440000000000001</v>
+      </c>
+      <c r="K818" s="6">
+        <v>18.22</v>
+      </c>
+      <c r="L818" s="6">
+        <v>15.76</v>
+      </c>
+      <c r="M818" s="6">
+        <v>8.01</v>
+      </c>
+      <c r="N818" s="6">
+        <v>2.63</v>
+      </c>
+      <c r="O818" s="6">
+        <v>0.54</v>
+      </c>
+      <c r="P818" s="6"/>
+      <c r="Q818" s="6"/>
+    </row>
+    <row r="819" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B819" s="3">
+        <v>2307650</v>
+      </c>
+      <c r="C819" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D819" s="3">
+        <v>2025</v>
+      </c>
+      <c r="E819" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F819" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G819" s="6">
+        <v>12.01</v>
+      </c>
+      <c r="H819" s="6">
+        <v>14.08</v>
+      </c>
+      <c r="I819" s="6">
+        <v>18.170000000000002</v>
+      </c>
+      <c r="J819" s="6">
+        <v>18.05</v>
+      </c>
+      <c r="K819" s="6">
+        <v>16.71</v>
+      </c>
+      <c r="L819" s="6">
+        <v>10.83</v>
+      </c>
+      <c r="M819" s="6">
+        <v>6.17</v>
+      </c>
+      <c r="N819" s="6">
+        <v>3.0700000000000003</v>
+      </c>
+      <c r="O819" s="6">
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="P819" s="6">
+        <v>0.21</v>
+      </c>
+      <c r="Q819" s="6"/>
+    </row>
   </sheetData>
   <autoFilter ref="B1:Q799"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
